--- a/Figure 5/Figure 5-F.xlsx
+++ b/Figure 5/Figure 5-F.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\图5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\iMetaOmics20260210\Figure 5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50B337FC-CE6F-432F-A994-22EB6AB84963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CACD3F5-F8E8-4CA7-AF0D-AFB5760B1A24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24840" yWindow="1260" windowWidth="15760" windowHeight="15580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28790" yWindow="4080" windowWidth="16730" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -90,7 +90,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -104,6 +104,12 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -128,7 +134,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -413,7 +419,8 @@
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B1" t="s">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
